--- a/qbittorrent/rss_manager.xlsx
+++ b/qbittorrent/rss_manager.xlsx
@@ -11,8 +11,8 @@
     <sheet name="RSS下载设置" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RSS订阅源'!$A$2:$G$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RSS下载设置'!$A$2:$L$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RSS订阅源'!$A$2:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RSS下载设置'!$A$2:$L$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -605,17 +605,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Anime/202601/可以帮忙洗干净吗 黑白字幕组</t>
+          <t>Anime/202601/勇者之屑 猎户压制部</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>可以帮忙洗干净吗 黑白字幕组</t>
+          <t>勇者之屑 猎户压制部</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://share.dmhy.org/topics/rss/rss.xml?keyword=%E5%8F%AF%E4%BB%A5%E5%B8%AE%E5%BF%99%E6%B4%97%E5%B9%B2%E5%87%80%E5%90%97+%E9%BB%91%E7%99%BD%E5%AD%97%E5%B9%95%E7%BB%84+%E7%AE%80%E6%97%A5</t>
+          <t>https://share.dmhy.org/topics/rss/rss.xml?keyword=%E5%8B%87%E8%80%85%E4%B9%8B%E5%B1%91+%E7%8C%8E%E6%88%B7%E5%8E%8B%E5%88%B6%E9%83%A8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -634,17 +634,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Anime/202601/异国日记-拨雪寻春</t>
+          <t>Anime/202601/可以帮忙洗干净吗 黑白字幕组</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>异国日记-拨雪寻春</t>
+          <t>可以帮忙洗干净吗 黑白字幕组</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://share.dmhy.org/topics/rss/rss.xml?keyword=%E5%BC%82%E5%9B%BD%E6%97%A5%E8%AE%B0+%E7%AE%80%E6%97%A5&amp;sort_id=0&amp;team_id=823&amp;order=date-desc</t>
+          <t>https://share.dmhy.org/topics/rss/rss.xml?keyword=%E5%8F%AF%E4%BB%A5%E5%B8%AE%E5%BF%99%E6%B4%97%E5%B9%B2%E5%87%80%E5%90%97+%E9%BB%91%E7%99%BD%E5%AD%97%E5%B9%95%E7%BB%84+%E7%AE%80%E6%97%A5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -663,22 +663,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Anime/202601/现在的是哪一个多闻 lolihouse</t>
+          <t>Anime/202601/名侦探光之美少女 雪飘工作室 1080p</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>现在的是哪一个多闻 lolihouse</t>
+          <t>名侦探光之美少女 雪飘工作室 1080p</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://share.dmhy.org/topics/rss/rss.xml?keyword=%E7%8E%B0%E5%9C%A8%E7%9A%84%E6%98%AF%E5%93%AA%E4%B8%80%E4%B8%AA%E5%A4%9A%E9%97%BB+lolihouse</t>
+          <t>https://share.dmhy.org/topics/rss/rss.xml?keyword=%E5%90%8D%E4%BE%A6%E6%8E%A2%E5%85%89%E4%B9%8B%E7%BE%8E%E5%B0%91%E5%A5%B3+%E9%9B%AA%E9%A3%98%E5%B7%A5%E4%BD%9C%E5%AE%A4+1080p</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -692,17 +692,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Anime/202601/相反的你和我 SweetSub</t>
+          <t>Anime/202601/异国日记-拨雪寻春</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>相反的你和我 SweetSub</t>
+          <t>异国日记-拨雪寻春</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://share.dmhy.org/topics/rss/rss.xml?keyword=%E7%9B%B8%E5%8F%8D%E7%9A%84%E4%BD%A0%E5%92%8C%E6%88%91+SweetSub+%E7%AE%80%E6%97%A5</t>
+          <t>https://share.dmhy.org/topics/rss/rss.xml?keyword=%E5%BC%82%E5%9B%BD%E6%97%A5%E8%AE%B0+%E7%AE%80%E6%97%A5&amp;sort_id=0&amp;team_id=823&amp;order=date-desc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -721,22 +721,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anime/202601/靠死亡游戏混饭吃 LoliHouse</t>
+          <t>Anime/202601/我推的孩子 绿茶字幕组 简日</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>靠死亡游戏混饭吃 LoliHouse</t>
+          <t>我推的孩子 绿茶字幕组 简日</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://share.dmhy.org/topics/rss/rss.xml?keyword=%E9%9D%A0%E6%AD%BB%E4%BA%A1%E6%B8%B8%E6%88%8F%E6%B7%B7%E9%A5%AD%E5%90%83+LoliHouse</t>
+          <t>https://share.dmhy.org/topics/rss/rss.xml?keyword=%E6%88%91%E6%8E%A8%E7%9A%84%E5%AD%A9%E5%AD%90+%E7%BB%BF%E8%8C%B6%E5%AD%97%E5%B9%95%E7%BB%84+%E7%AE%80%E6%97%A5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -750,55 +750,200 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anime/202604</t>
+          <t>Anime/202601/现在的是哪一个多闻 lolihouse</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>202604</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>现在的是哪一个多闻 lolihouse</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://share.dmhy.org/topics/rss/rss.xml?keyword=%E7%8E%B0%E5%9C%A8%E7%9A%84%E6%98%AF%E5%93%AA%E4%B8%80%E4%B8%AA%E5%A4%9A%E9%97%BB+lolihouse</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>文件夹</t>
+          <t>订阅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Anime/202604/JOJO的奇妙冒险 飙马野郎 桜都字幕组</t>
+          <t>Anime/202601/相反的你和我 SweetSub</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JOJO的奇妙冒险 飙马野郎 桜都字幕组</t>
+          <t>相反的你和我 SweetSub</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://share.dmhy.org/topics/rss/rss.xml?keyword=JOJO%E7%9A%84%E5%A5%87%E5%A6%99%E5%86%92%E9%99%A9+%E9%A3%99%E9%A9%AC%E9%87%8E%E9%83%8E+%E7%AE%80%E4%BD%93+%E6%A1%9C%E9%83%BD%E5%AD%97%E5%B9%95%E7%BB%84</t>
+          <t>https://share.dmhy.org/topics/rss/rss.xml?keyword=%E7%9B%B8%E5%8F%8D%E7%9A%84%E4%BD%A0%E5%92%8C%E6%88%91+SweetSub+%E7%AE%80%E6%97%A5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>订阅</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Anime/202601/透明男与人类女 幻樱字幕组</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>透明男与人类女 幻樱字幕组</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://share.dmhy.org/topics/rss/rss.xml?keyword=%E9%80%8F%E6%98%8E%E7%94%B7%E4%B8%8E%E4%BA%BA%E7%B1%BB%E5%A5%B3+%E5%B9%BB%E6%A8%B1%E5%AD%97%E5%B9%95%E7%BB%84</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>订阅</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Anime/202601/靠死亡游戏混饭吃 LoliHouse</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>靠死亡游戏混饭吃 LoliHouse</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://share.dmhy.org/topics/rss/rss.xml?keyword=%E9%9D%A0%E6%AD%BB%E4%BA%A1%E6%B8%B8%E6%88%8F%E6%B7%B7%E9%A5%AD%E5%90%83+LoliHouse</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>订阅</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Anime/202601/魔都精兵的奴隶 第二季 桜都字幕组 简体</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>魔都精兵的奴隶 第二季 桜都字幕组 简体</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://share.dmhy.org/topics/rss/rss.xml?keyword=%E9%AD%94%E9%83%BD%E7%B2%BE%E5%85%B5%E7%9A%84%E5%A5%B4%E9%9A%B6+%E7%AC%AC%E4%BA%8C%E5%AD%A3+%E6%A1%9C%E9%83%BD%E5%AD%97%E5%B9%95%E7%BB%84+%E7%AE%80%E4%BD%93</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>订阅</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Anime/202604</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>文件夹</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Anime/202604/JOJO的奇妙冒险 飙马野郎 桜都字幕组</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JOJO的奇妙冒险 飙马野郎 桜都字幕组</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://share.dmhy.org/topics/rss/rss.xml?keyword=JOJO%E7%9A%84%E5%A5%87%E5%A6%99%E5%86%92%E9%99%A9+%E9%A3%99%E9%A9%AC%E9%87%8E%E9%83%8E+%E7%AE%80%E4%BD%93+%E6%A1%9C%E9%83%BD%E5%AD%97%E5%B9%95%E7%BB%84</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
         <v>1</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>订阅</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G12"/>
+  <autoFilter ref="A2:G17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -809,7 +954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -997,7 +1142,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>202601/可以帮忙洗干净吗</t>
+          <t>202601/勇者之屑</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1023,12 +1168,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Anime/202601/可以帮忙洗干净吗 黑白字幕组</t>
+          <t>Anime/202601/勇者之屑 猎户压制部</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>E:\Anime\202601\能帮我弄干净吗</t>
+          <t>E:\Anime\202601\勇者之屑</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1041,7 +1186,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>202601/异国日记</t>
+          <t>202601/可以帮忙洗干净吗</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1067,12 +1212,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Anime/202601/异国日记-拨雪寻春</t>
+          <t>Anime/202601/可以帮忙洗干净吗 黑白字幕组</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>E:\Anime\202601\异国日记</t>
+          <t>E:\Anime\202601\能帮我弄干净吗</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1085,7 +1230,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>202601/现在的是哪一个多闻</t>
+          <t>202601/名侦探光之美少女</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1111,12 +1256,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Anime/202601/现在的是哪一个多闻 lolihouse</t>
+          <t>Anime/202601/名侦探光之美少女 雪飘工作室 1080p</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>E:\Anime\202601\現在的是哪一個多聞</t>
+          <t>E:\Anime\202601\名侦探光之美少女！</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1129,7 +1274,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>202601/相反的你和我</t>
+          <t>202601/异国日记</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1155,12 +1300,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Anime/202601/相反的你和我 SweetSub</t>
+          <t>Anime/202601/异国日记-拨雪寻春</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>E:\Anime\202601\相反的你和我</t>
+          <t>E:\Anime\202601\异国日记</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1173,7 +1318,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>202601/靠死亡游戏混饭吃</t>
+          <t>202601/我推的孩子</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1199,12 +1344,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Anime/202601/靠死亡游戏混饭吃 LoliHouse</t>
+          <t>Anime/202601/我推的孩子 绿茶字幕组 简日</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>E:\Anime\202601\以死亡游戏为生。</t>
+          <t>E:\Anime\202601\【我推的孩子】</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1217,7 +1362,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>202604/JOJO的奇妙冒险 飙马野郎</t>
+          <t>202601/现在的是哪一个多闻</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1243,12 +1388,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Anime/202604/JOJO的奇妙冒险 飙马野郎 桜都字幕组</t>
+          <t>Anime/202601/现在的是哪一个多闻 lolihouse</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>E:\Anime\202604\JOJO的奇妙冒险 飙马野郎</t>
+          <t>E:\Anime\202601\現在的是哪一個多聞</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1258,8 +1403,228 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>202601/相反的你和我</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Anime/202601/相反的你和我 SweetSub</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>E:\Anime\202601\相反的你和我</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>202601/透明男与人类女</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Anime/202601/透明男与人类女 幻樱字幕组</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>E:\Anime\202601\透明男与人类女</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>202601/靠死亡游戏混饭吃</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Anime/202601/靠死亡游戏混饭吃 LoliHouse</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>E:\Anime\202601\以死亡游戏为生。</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>202601/魔都精兵的奴隶 第二季</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Anime/202601/魔都精兵的奴隶 第二季 桜都字幕组 简体</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>E:\Anime\202601\魔都精兵的奴隶 第二季</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>202604/JOJO的奇妙冒险 飙马野郎</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Anime/202604/JOJO的奇妙冒险 飙马野郎 桜都字幕组</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>E:\Anime\202604\JOJO的奇妙冒险 飙马野郎</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:L9"/>
+  <autoFilter ref="A2:L14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>